--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486920_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486920_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.839700000000001</v>
+        <v>8.713699999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>4.5044</v>
+        <v>4.6749</v>
       </c>
       <c r="F2" t="n">
-        <v>4.3353</v>
+        <v>4.0389</v>
       </c>
       <c r="G2" t="n">
         <v>6.1228</v>
@@ -610,13 +610,13 @@
         <v>2.4641</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1275</v>
+        <v>1.0016</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1122</v>
+        <v>0.2827</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0153</v>
+        <v>0.7189</v>
       </c>
       <c r="V2" t="n">
         <v>1.1786</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.8075</v>
+        <v>5.4937</v>
       </c>
       <c r="E3" t="n">
-        <v>2.4674</v>
+        <v>2.1536</v>
       </c>
       <c r="F3" t="n">
         <v>3.3401</v>
@@ -688,10 +688,10 @@
         <v>2.2588</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7246</v>
+        <v>0.4108</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1045</v>
+        <v>-0.2093</v>
       </c>
       <c r="U3" t="n">
         <v>0.6201</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.5862</v>
+        <v>4.2641</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0931</v>
+        <v>1.682</v>
       </c>
       <c r="F4" t="n">
-        <v>2.4931</v>
+        <v>2.5821</v>
       </c>
       <c r="G4" t="n">
         <v>0.8299</v>
@@ -766,13 +766,13 @@
         <v>2.0534</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3669</v>
+        <v>0.311</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4534</v>
+        <v>0.1355</v>
       </c>
       <c r="U4" t="n">
-        <v>0.08649999999999999</v>
+        <v>0.1755</v>
       </c>
       <c r="V4" t="n">
         <v>1.0698</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.1477</v>
+        <v>2.8701</v>
       </c>
       <c r="E5" t="n">
-        <v>3.9348</v>
+        <v>3.6869</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.7871</v>
+        <v>-0.8167</v>
       </c>
       <c r="G5" t="n">
         <v>2.3051</v>
@@ -844,13 +844,13 @@
         <v>1.8481</v>
       </c>
       <c r="S5" t="n">
-        <v>1.3518</v>
+        <v>1.0742</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8096</v>
+        <v>0.5616</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5422</v>
+        <v>0.5125</v>
       </c>
       <c r="V5" t="n">
         <v>-2.3573</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. ILINCIC</t>
+          <t>L. FERRANDO ORTELLS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4902</v>
+        <v>2.803</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3567</v>
+        <v>-0.2773</v>
       </c>
       <c r="F6" t="n">
-        <v>2.1335</v>
+        <v>3.0802</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6231</v>
+        <v>3.1185</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9703000000000001</v>
+        <v>2.9265</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3472</v>
+        <v>0.192</v>
       </c>
       <c r="J6" t="n">
-        <v>1.7198</v>
+        <v>2.5154</v>
       </c>
       <c r="K6" t="n">
-        <v>1.7198</v>
+        <v>2.6736</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-0.1582</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.0967</v>
+        <v>0.603</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7495000000000001</v>
+        <v>0.2528</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3472</v>
+        <v>0.3502</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.0534</v>
+        <v>-2.2588</v>
       </c>
       <c r="Q6" t="n">
         <v>-4.1068</v>
       </c>
       <c r="R6" t="n">
-        <v>2.0534</v>
+        <v>1.8481</v>
       </c>
       <c r="S6" t="n">
-        <v>2.0437</v>
+        <v>0.6558</v>
       </c>
       <c r="T6" t="n">
-        <v>1.5651</v>
+        <v>0.1355</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4786</v>
+        <v>0.5203</v>
       </c>
       <c r="V6" t="n">
-        <v>1.8768</v>
+        <v>1.2875</v>
       </c>
       <c r="W6" t="n">
         <v>1.1786</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6982</v>
+        <v>0.1088</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. FERRANDO ORTELLS</t>
+          <t>D. ILINCIC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.191</v>
+        <v>1.2959</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8003</v>
+        <v>-0.6893</v>
       </c>
       <c r="F7" t="n">
-        <v>2.9913</v>
+        <v>1.9853</v>
       </c>
       <c r="G7" t="n">
-        <v>3.1185</v>
+        <v>0.6231</v>
       </c>
       <c r="H7" t="n">
-        <v>2.9265</v>
+        <v>0.9703000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>0.192</v>
+        <v>-0.3472</v>
       </c>
       <c r="J7" t="n">
-        <v>2.5154</v>
+        <v>1.7198</v>
       </c>
       <c r="K7" t="n">
-        <v>2.6736</v>
+        <v>1.7198</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.1582</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.603</v>
+        <v>-1.0967</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2528</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3502</v>
+        <v>-0.3472</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.2588</v>
+        <v>-2.0534</v>
       </c>
       <c r="Q7" t="n">
         <v>-4.1068</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8481</v>
+        <v>2.0534</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0438</v>
+        <v>0.8494</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3875</v>
+        <v>0.5191</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4313</v>
+        <v>0.3304</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2875</v>
+        <v>1.8768</v>
       </c>
       <c r="W7" t="n">
         <v>1.1786</v>
       </c>
       <c r="X7" t="n">
-        <v>0.1088</v>
+        <v>0.6982</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. SOLER CIRUJEDA</t>
+          <t>A. BELLVER VALIENTE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9192</v>
+        <v>0.9636</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.591</v>
+        <v>-0.2054</v>
       </c>
       <c r="F8" t="n">
-        <v>1.5102</v>
+        <v>1.169</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0595</v>
+        <v>-1.1063</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5222</v>
+        <v>-0.2013</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5816</v>
+        <v>-0.905</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.3275</v>
+        <v>0.1007</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.3275</v>
+        <v>0.7981</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-0.6974</v>
       </c>
       <c r="M8" t="n">
-        <v>0.387</v>
+        <v>-1.2071</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1947</v>
+        <v>-0.9994</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5816</v>
+        <v>-0.2077</v>
       </c>
       <c r="P8" t="n">
-        <v>0.616</v>
+        <v>2.0534</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.616</v>
+        <v>2.0534</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2437</v>
+        <v>0.0165</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2635</v>
+        <v>-0.3062</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5072</v>
+        <v>0.3226</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. BELLVER VALIENTE</t>
+          <t>J. SOLER CIRUJEDA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5748</v>
+        <v>0.8895999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6238</v>
+        <v>-0.591</v>
       </c>
       <c r="F9" t="n">
-        <v>1.1986</v>
+        <v>1.4806</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.1063</v>
+        <v>0.0595</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.2013</v>
+        <v>-0.5222</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.905</v>
+        <v>0.5816</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1007</v>
+        <v>-0.3275</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7981</v>
+        <v>-0.3275</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6974</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.2071</v>
+        <v>0.387</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9994</v>
+        <v>-0.1947</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2077</v>
+        <v>0.5816</v>
       </c>
       <c r="P9" t="n">
-        <v>2.0534</v>
+        <v>0.616</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.0534</v>
+        <v>0.616</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3723</v>
+        <v>0.2141</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7246</v>
+        <v>-0.2635</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3523</v>
+        <v>0.4776</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2729</v>
+        <v>-0.5052</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.5559</v>
+        <v>-1.6992</v>
       </c>
       <c r="F10" t="n">
-        <v>1.2829</v>
+        <v>1.194</v>
       </c>
       <c r="G10" t="n">
         <v>-0.2678</v>
@@ -1234,13 +1234,13 @@
         <v>2.2588</v>
       </c>
       <c r="S10" t="n">
-        <v>1.0565</v>
+        <v>0.8242</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8096</v>
+        <v>0.6662</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2469</v>
+        <v>0.158</v>
       </c>
       <c r="V10" t="n">
         <v>-0.2402</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.5184</v>
+        <v>-1.4295</v>
       </c>
       <c r="E11" t="n">
         <v>-1.0727</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4457</v>
+        <v>-0.3568</v>
       </c>
       <c r="G11" t="n">
         <v>-0.148</v>
@@ -1312,13 +1312,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3437</v>
+        <v>-0.2547</v>
       </c>
       <c r="T11" t="n">
         <v>-0.2635</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.08019999999999999</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.5859</v>
+        <v>-2.5876</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.9993</v>
+        <v>-3.2085</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4134</v>
+        <v>0.6209</v>
       </c>
       <c r="G12" t="n">
         <v>-0.0728</v>
@@ -1390,13 +1390,13 @@
         <v>2.6694</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1461</v>
+        <v>0.1443</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0272</v>
+        <v>-0.2364</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1733</v>
+        <v>0.3808</v>
       </c>
       <c r="V12" t="n">
         <v>-2.2484</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.6855</v>
+        <v>-4.9484</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.0314</v>
+        <v>-4.4425</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.6541</v>
+        <v>-0.5059</v>
       </c>
       <c r="G13" t="n">
         <v>-3.7925</v>
@@ -1468,13 +1468,13 @@
         <v>2.4641</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9278999999999999</v>
+        <v>-0.1908</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8563</v>
+        <v>-0.2674</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0716</v>
+        <v>0.0766</v>
       </c>
       <c r="V13" t="n">
         <v>-0.3491</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>17.4936</v>
+        <v>17.823</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.3179999999999987</v>
+        <v>0.01150000000000073</v>
       </c>
       <c r="F14" t="n">
-        <v>17.8115</v>
+        <v>17.81169999999999</v>
       </c>
       <c r="G14" t="n">
         <v>11.5224</v>
@@ -1546,13 +1546,13 @@
         <v>22.5876</v>
       </c>
       <c r="S14" t="n">
-        <v>4.726899999999999</v>
+        <v>5.056400000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4250000000000002</v>
+        <v>0.7543</v>
       </c>
       <c r="U14" t="n">
-        <v>4.301900000000001</v>
+        <v>4.302</v>
       </c>
       <c r="V14" t="n">
         <v>0.2176999999999997</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.8874</v>
+        <v>2.0564</v>
       </c>
       <c r="E15" t="n">
-        <v>1.258</v>
+        <v>1.9903</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6294</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="G15" t="n">
         <v>-0.1101</v>
@@ -1624,13 +1624,13 @@
         <v>2.2588</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0189</v>
+        <v>0.1501</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.3174</v>
+        <v>-0.5852000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>1.2986</v>
+        <v>0.7354000000000001</v>
       </c>
       <c r="V15" t="n">
         <v>2.8377</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0475</v>
+        <v>1.5828</v>
       </c>
       <c r="E16" t="n">
-        <v>1.0923</v>
+        <v>1.3015</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0448</v>
+        <v>0.2813</v>
       </c>
       <c r="G16" t="n">
         <v>0.2955</v>
@@ -1702,13 +1702,13 @@
         <v>1.8481</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.3363</v>
+        <v>-0.801</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9222</v>
+        <v>-0.713</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4141</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="V16" t="n">
         <v>0.2402</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1649</v>
+        <v>0.2065</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.6348</v>
+        <v>-0.5302</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4699</v>
+        <v>0.7367</v>
       </c>
       <c r="G17" t="n">
         <v>3.0257</v>
@@ -1780,13 +1780,13 @@
         <v>2.2588</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.012</v>
+        <v>0.3593</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0272</v>
+        <v>0.0774</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0152</v>
+        <v>0.282</v>
       </c>
       <c r="V17" t="n">
         <v>-2.3573</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9124</v>
+        <v>-0.4748</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1361</v>
+        <v>0.0731</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7763</v>
+        <v>-0.5479000000000001</v>
       </c>
       <c r="G18" t="n">
         <v>-0.8047</v>
@@ -1858,13 +1858,13 @@
         <v>1.2321</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.2309</v>
+        <v>-0.7933</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5928</v>
+        <v>-0.3836</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6381</v>
+        <v>-0.4097</v>
       </c>
       <c r="V18" t="n">
         <v>-0.1088</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. GALLEGO MOGRO</t>
+          <t>M. ENABULELE OGUNSUYI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3382</v>
+        <v>-1.5075</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.7064</v>
+        <v>-0.6039</v>
       </c>
       <c r="F19" t="n">
-        <v>1.3682</v>
+        <v>-0.9035</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.9568</v>
+        <v>0.479</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.0146</v>
+        <v>1.0024</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.9422</v>
+        <v>-0.5234</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.3658</v>
+        <v>2.4961</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.655</v>
+        <v>2.4172</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.7108</v>
+        <v>0.0789</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.591</v>
+        <v>-2.0171</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.3596</v>
+        <v>-1.4148</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2314</v>
+        <v>-0.6022999999999999</v>
       </c>
       <c r="P19" t="n">
-        <v>1.0267</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q19" t="n">
         <v>-2.0534</v>
       </c>
       <c r="R19" t="n">
-        <v>3.0801</v>
+        <v>1.8481</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3516</v>
+        <v>-0.8427</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4725</v>
+        <v>-0.6975</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1208</v>
+        <v>-0.1452</v>
       </c>
       <c r="V19" t="n">
-        <v>0.2402</v>
+        <v>-0.9384</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2402</v>
+        <v>-0.3491</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.5893</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. ENABULELE OGUNSUYI</t>
+          <t>S. GALLEGO MOGRO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4761</v>
+        <v>-1.6241</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.3947</v>
+        <v>-3.2295</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.0814</v>
+        <v>1.6054</v>
       </c>
       <c r="G20" t="n">
-        <v>0.479</v>
+        <v>-2.9568</v>
       </c>
       <c r="H20" t="n">
-        <v>1.0024</v>
+        <v>-2.0146</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5234</v>
+        <v>-0.9422</v>
       </c>
       <c r="J20" t="n">
-        <v>2.4961</v>
+        <v>-1.3658</v>
       </c>
       <c r="K20" t="n">
-        <v>2.4172</v>
+        <v>-0.655</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0789</v>
+        <v>-0.7108</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.0171</v>
+        <v>-1.591</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.4148</v>
+        <v>-1.3596</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6022999999999999</v>
+        <v>-0.2314</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.2053</v>
+        <v>1.0267</v>
       </c>
       <c r="Q20" t="n">
         <v>-2.0534</v>
       </c>
       <c r="R20" t="n">
-        <v>1.8481</v>
+        <v>3.0801</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8114</v>
+        <v>0.0658</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4883</v>
+        <v>-0.0505</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.323</v>
+        <v>0.1163</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.9384</v>
+        <v>0.2402</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.3491</v>
+        <v>0.2402</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5893</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.8661</v>
+        <v>-1.7005</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.2922</v>
+        <v>-2.9784</v>
       </c>
       <c r="F21" t="n">
-        <v>1.4261</v>
+        <v>1.2779</v>
       </c>
       <c r="G21" t="n">
         <v>-3.0738</v>
@@ -2092,13 +2092,13 @@
         <v>2.0534</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5172</v>
+        <v>-0.3516</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9881</v>
+        <v>-0.6743</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4709</v>
+        <v>0.3226</v>
       </c>
       <c r="V21" t="n">
         <v>0.6982</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4863</v>
+        <v>-2.6729</v>
       </c>
       <c r="E22" t="n">
         <v>-2.8962</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4099</v>
+        <v>0.2233</v>
       </c>
       <c r="G22" t="n">
         <v>-3.3732</v>
@@ -2170,13 +2170,13 @@
         <v>1.6427</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0307</v>
+        <v>-0.1559</v>
       </c>
       <c r="T22" t="n">
         <v>-0.159</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1896</v>
+        <v>0.003</v>
       </c>
       <c r="V22" t="n">
         <v>0.2402</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.5525</v>
+        <v>-3.1445</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.3174</v>
+        <v>-2.1082</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.2351</v>
+        <v>-1.0363</v>
       </c>
       <c r="G23" t="n">
         <v>-2.7904</v>
@@ -2248,13 +2248,13 @@
         <v>1.6427</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.7272</v>
+        <v>-1.3193</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1198</v>
+        <v>-0.9106</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6074000000000001</v>
+        <v>-0.4087</v>
       </c>
       <c r="V23" t="n">
         <v>0.3491</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.1349</v>
+        <v>-3.6833</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.7927</v>
+        <v>-3.6881</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.3422</v>
+        <v>0.0048</v>
       </c>
       <c r="G24" t="n">
         <v>-1.6626</v>
@@ -2326,13 +2326,13 @@
         <v>2.0534</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.3572</v>
+        <v>-0.9056</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6587</v>
+        <v>-0.5541</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6985</v>
+        <v>-0.3515</v>
       </c>
       <c r="V24" t="n">
         <v>0.9384</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.4971</v>
+        <v>-5.8343</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.9913</v>
+        <v>-5.1419</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.5058</v>
+        <v>-0.6924</v>
       </c>
       <c r="G25" t="n">
         <v>-0.5508999999999999</v>
@@ -2404,13 +2404,13 @@
         <v>1.6427</v>
       </c>
       <c r="S25" t="n">
-        <v>1.9019</v>
+        <v>0.5647</v>
       </c>
       <c r="T25" t="n">
-        <v>1.4992</v>
+        <v>0.3486</v>
       </c>
       <c r="U25" t="n">
-        <v>0.4027</v>
+        <v>0.2161</v>
       </c>
       <c r="V25" t="n">
         <v>-2.3573</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-17.4936</v>
+        <v>-16.7962</v>
       </c>
       <c r="E26" t="n">
         <v>-17.8115</v>
       </c>
       <c r="F26" t="n">
-        <v>0.3178999999999996</v>
+        <v>1.0155</v>
       </c>
       <c r="G26" t="n">
         <v>-11.5223</v>
@@ -2482,13 +2482,13 @@
         <v>21.5609</v>
       </c>
       <c r="S26" t="n">
-        <v>-4.726900000000001</v>
+        <v>-4.0295</v>
       </c>
       <c r="T26" t="n">
-        <v>-4.301799999999999</v>
+        <v>-4.3018</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.4249000000000001</v>
+        <v>0.2723</v>
       </c>
       <c r="V26" t="n">
         <v>-0.2178</v>
